--- a/backend/raw_materials_pricing.xlsx
+++ b/backend/raw_materials_pricing.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IS-9295 Pipe diameters and weights per IS-1239</t>
+          <t>IS-9295 Pipe diameters and weights per IS-9192</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>PIPE SPECIFICATIONS (IS-9295 &amp; IS-1239)</t>
+          <t>PIPE SPECIFICATIONS (IS-9295 &amp; IS-9192)</t>
         </is>
       </c>
     </row>

--- a/backend/raw_materials_pricing.xlsx
+++ b/backend/raw_materials_pricing.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IS-9295 Pipe diameters and weights per IS-9192</t>
+          <t>IS-9295 Pipe diameters and weights per IS-9295</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>PIPE SPECIFICATIONS (IS-9295 &amp; IS-9192)</t>
+          <t>PIPE SPECIFICATIONS (IS-9295 &amp; IS-9295)</t>
         </is>
       </c>
     </row>

--- a/backend/raw_materials_pricing.xlsx
+++ b/backend/raw_materials_pricing.xlsx
@@ -984,7 +984,7 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>63.5</v>
+        <v>60.8</v>
       </c>
       <c r="B6" s="7" t="n">
         <v>4.11</v>
